--- a/Feuilles/A bout.xlsx
+++ b/Feuilles/A bout.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A1D9FF-D96D-B043-B0EA-88762AC2C3FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4DC93A-6C3A-EC4A-BAA5-994B1DED618A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10360" yWindow="2140" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
+    <workbookView xWindow="6080" yWindow="2140" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>MES</t>
   </si>
@@ -77,9 +77,6 @@
     <t>COUPLET 3</t>
   </si>
   <si>
-    <t>Ha Ha Ha…</t>
-  </si>
-  <si>
     <t>PONT FX</t>
   </si>
   <si>
@@ -89,14 +86,20 @@
     <t>AD LIB</t>
   </si>
   <si>
-    <t>Ha Ha Ha Ha…</t>
+    <t>LOOP</t>
+  </si>
+  <si>
+    <t>Ha Ha Ha... B</t>
+  </si>
+  <si>
+    <t>Ha Ha Ha... A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -109,6 +112,13 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -132,9 +142,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -469,10 +480,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B34C31-2D9C-7940-9F39-E67ACD52E89F}">
-  <dimension ref="A1:D224"/>
+  <dimension ref="A1:E224"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="11.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -485,8 +499,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -500,7 +517,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -511,7 +528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -522,7 +539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -533,7 +550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -544,7 +561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -555,7 +572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -566,7 +583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -577,7 +594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -588,7 +605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -599,7 +616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -610,7 +627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -621,7 +638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -632,7 +649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -643,7 +660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -788,8 +805,8 @@
       <c r="C28">
         <v>0</v>
       </c>
-      <c r="D28" t="s">
-        <v>12</v>
+      <c r="D28" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
@@ -1117,7 +1134,7 @@
         <v>0</v>
       </c>
       <c r="D57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
@@ -1208,7 +1225,7 @@
         <v>1</v>
       </c>
       <c r="D65" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
@@ -1586,7 +1603,7 @@
         <v>0</v>
       </c>
       <c r="D98" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">

--- a/Feuilles/A bout.xlsx
+++ b/Feuilles/A bout.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4DC93A-6C3A-EC4A-BAA5-994B1DED618A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD354AC-65CD-B748-955D-65AA5E6BDB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6080" yWindow="2140" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
@@ -853,7 +853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -864,7 +864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -875,7 +875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -900,7 +900,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -922,7 +922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -933,7 +933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -944,7 +944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -955,7 +955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -977,7 +977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1001,8 +1001,11 @@
       <c r="D45" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1013,7 +1016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1024,7 +1027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1035,7 +1038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1046,7 +1049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1057,7 +1060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1068,7 +1071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1079,7 +1082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1090,7 +1093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1101,7 +1104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1112,7 +1115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1123,7 +1126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1136,8 +1139,11 @@
       <c r="D57" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1148,7 +1154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1159,7 +1165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1170,7 +1176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1181,7 +1187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1192,7 +1198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1203,7 +1209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1214,7 +1220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1228,7 +1234,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1242,7 +1248,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1253,7 +1259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1264,7 +1270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -1275,7 +1281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -1286,7 +1292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1297,7 +1303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -1308,7 +1314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -1319,7 +1325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -1332,8 +1338,11 @@
       <c r="D74" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -1344,7 +1353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -1355,7 +1364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -1366,7 +1375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -1377,7 +1386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -1388,7 +1397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -1399,7 +1408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -1410,7 +1419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -1423,8 +1432,11 @@
       <c r="D82" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -1435,7 +1447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -1446,7 +1458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -1457,7 +1469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -1468,7 +1480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -1479,7 +1491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -1490,7 +1502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -1501,7 +1513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -1514,8 +1526,11 @@
       <c r="D90" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -1526,7 +1541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -1537,7 +1552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -1548,7 +1563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -1559,7 +1574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -1570,7 +1585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
@@ -1581,7 +1596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>96</v>
       </c>
@@ -1592,7 +1607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -1605,8 +1620,11 @@
       <c r="D98" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
@@ -1617,7 +1635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>99</v>
       </c>
@@ -1628,7 +1646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>100</v>
       </c>
@@ -1639,7 +1657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>101</v>
       </c>
@@ -1650,7 +1668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>102</v>
       </c>
@@ -1661,7 +1679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>103</v>
       </c>
@@ -1672,7 +1690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>104</v>
       </c>
@@ -1683,7 +1701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>105</v>
       </c>
@@ -1694,7 +1712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>106</v>
       </c>
@@ -1705,7 +1723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>107</v>
       </c>
@@ -1718,8 +1736,11 @@
       <c r="D108" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>108</v>
       </c>
@@ -1730,7 +1751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>109</v>
       </c>
@@ -1741,7 +1762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>110</v>
       </c>
@@ -1752,7 +1773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>111</v>
       </c>
